--- a/Book 7.xlsx
+++ b/Book 7.xlsx
@@ -583,7 +583,7 @@
     </row>
     <row r="19">
       <c r="A19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
@@ -591,7 +591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>

--- a/Book 7.xlsx
+++ b/Book 7.xlsx
@@ -455,7 +455,7 @@
     </row>
     <row r="3">
       <c r="A3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -463,7 +463,7 @@
     </row>
     <row r="4">
       <c r="A4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="5">
       <c r="A5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -479,7 +479,7 @@
     </row>
     <row r="6">
       <c r="A6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -487,7 +487,7 @@
     </row>
     <row r="7">
       <c r="A7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="8">
       <c r="A8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="9">
       <c r="A9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -511,7 +511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="11">
       <c r="A11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -527,7 +527,7 @@
     </row>
     <row r="12">
       <c r="A12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -535,7 +535,7 @@
     </row>
     <row r="13">
       <c r="A13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="14">
       <c r="A14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>14</v>
@@ -551,7 +551,7 @@
     </row>
     <row r="15">
       <c r="A15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="16">
       <c r="A16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="17">
       <c r="A17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
@@ -575,7 +575,7 @@
     </row>
     <row r="18">
       <c r="A18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>18</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="21">
       <c r="A21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="22">
       <c r="A22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
@@ -631,11 +631,14 @@
     </row>
     <row r="25">
       <c r="A25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
       </c>
+    </row>
+    <row r="27">
+      <c r="B27"/>
     </row>
   </sheetData>
 </worksheet>
